--- a/ig/DM-37/CodeSystem-TRE-R212-Equipement.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-R212-Equipement.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="483">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -751,13 +751,19 @@
     <t>098</t>
   </si>
   <si>
-    <t>Bassin thérapeutique pour balnéothérapie (&lt;20m2)</t>
+    <t>Bassin thérapeutique pour balnéothérapie (&lt;25m2)</t>
+  </si>
+  <si>
+    <t>Ensemble de soins reposant sur l'immersion du corps ou d'une partie du corps dans un bassin d'eau (inférieur à 25 m²) à des fins thérapeutiques</t>
   </si>
   <si>
     <t>099</t>
   </si>
   <si>
-    <t>Piscine pour balnéothérapie (&gt;20m2)</t>
+    <t>Bassin thérapeutique pour balnéothérapie (&gt;=25m2)</t>
+  </si>
+  <si>
+    <t>Plateau technique spécialisé constitué par un bassin permettant l'immersion du corps ou d'une partie du corps dans un bassin d'eau (supérieur à 25 m²) à des fins thérapeutiques, équipé de dispositifs de levage et de rampes d'accès au bassin</t>
   </si>
   <si>
     <t>100</t>
@@ -1445,6 +1451,18 @@
   </si>
   <si>
     <t>Arthromoteurs membres supérieurs (épaules, coudes)</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>Salle hybride</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Vidéo assistance</t>
   </si>
 </sst>
 </file>
@@ -1818,7 +1836,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D211"/>
+  <dimension ref="A1:D213"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3009,29 +3027,33 @@
       <c r="C99" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="D99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>246</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="D100" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="D100" t="s" s="2">
+        <v>249</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D101" s="2"/>
     </row>
@@ -3040,10 +3062,10 @@
         <v>49</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D102" s="2"/>
     </row>
@@ -3052,10 +3074,10 @@
         <v>49</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D103" s="2"/>
     </row>
@@ -3064,10 +3086,10 @@
         <v>49</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D104" s="2"/>
     </row>
@@ -3076,10 +3098,10 @@
         <v>49</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D105" s="2"/>
     </row>
@@ -3088,10 +3110,10 @@
         <v>49</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" s="2"/>
     </row>
@@ -3100,10 +3122,10 @@
         <v>49</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D107" s="2"/>
     </row>
@@ -3112,10 +3134,10 @@
         <v>49</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D108" s="2"/>
     </row>
@@ -3124,10 +3146,10 @@
         <v>49</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D109" s="2"/>
     </row>
@@ -3136,10 +3158,10 @@
         <v>49</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D110" s="2"/>
     </row>
@@ -3148,10 +3170,10 @@
         <v>49</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D111" s="2"/>
     </row>
@@ -3160,10 +3182,10 @@
         <v>49</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D112" s="2"/>
     </row>
@@ -3172,10 +3194,10 @@
         <v>49</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D113" s="2"/>
     </row>
@@ -3184,10 +3206,10 @@
         <v>49</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D114" s="2"/>
     </row>
@@ -3196,10 +3218,10 @@
         <v>49</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D115" s="2"/>
     </row>
@@ -3208,10 +3230,10 @@
         <v>49</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D116" s="2"/>
     </row>
@@ -3220,10 +3242,10 @@
         <v>49</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D117" s="2"/>
     </row>
@@ -3232,10 +3254,10 @@
         <v>49</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D118" s="2"/>
     </row>
@@ -3244,10 +3266,10 @@
         <v>49</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D119" s="2"/>
     </row>
@@ -3256,10 +3278,10 @@
         <v>49</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D120" s="2"/>
     </row>
@@ -3268,10 +3290,10 @@
         <v>49</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D121" s="2"/>
     </row>
@@ -3280,10 +3302,10 @@
         <v>49</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D122" s="2"/>
     </row>
@@ -3292,10 +3314,10 @@
         <v>49</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D123" s="2"/>
     </row>
@@ -3304,10 +3326,10 @@
         <v>49</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D124" s="2"/>
     </row>
@@ -3316,10 +3338,10 @@
         <v>49</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D125" s="2"/>
     </row>
@@ -3328,10 +3350,10 @@
         <v>49</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D126" s="2"/>
     </row>
@@ -3340,10 +3362,10 @@
         <v>49</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D127" s="2"/>
     </row>
@@ -3352,10 +3374,10 @@
         <v>49</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D128" s="2"/>
     </row>
@@ -3364,10 +3386,10 @@
         <v>49</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D129" s="2"/>
     </row>
@@ -3376,10 +3398,10 @@
         <v>49</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D130" s="2"/>
     </row>
@@ -3388,10 +3410,10 @@
         <v>49</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D131" s="2"/>
     </row>
@@ -3400,10 +3422,10 @@
         <v>49</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D132" s="2"/>
     </row>
@@ -3412,10 +3434,10 @@
         <v>49</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D133" s="2"/>
     </row>
@@ -3424,10 +3446,10 @@
         <v>49</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D134" s="2"/>
     </row>
@@ -3436,10 +3458,10 @@
         <v>49</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D135" s="2"/>
     </row>
@@ -3448,10 +3470,10 @@
         <v>49</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D136" s="2"/>
     </row>
@@ -3460,10 +3482,10 @@
         <v>49</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D137" s="2"/>
     </row>
@@ -3472,10 +3494,10 @@
         <v>49</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D138" s="2"/>
     </row>
@@ -3484,10 +3506,10 @@
         <v>49</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D139" s="2"/>
     </row>
@@ -3496,10 +3518,10 @@
         <v>49</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D140" s="2"/>
     </row>
@@ -3508,10 +3530,10 @@
         <v>49</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D141" s="2"/>
     </row>
@@ -3520,10 +3542,10 @@
         <v>49</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D142" s="2"/>
     </row>
@@ -3532,10 +3554,10 @@
         <v>49</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D143" s="2"/>
     </row>
@@ -3544,10 +3566,10 @@
         <v>49</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D144" s="2"/>
     </row>
@@ -3556,10 +3578,10 @@
         <v>49</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D145" s="2"/>
     </row>
@@ -3568,10 +3590,10 @@
         <v>49</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D146" s="2"/>
     </row>
@@ -3580,10 +3602,10 @@
         <v>49</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D147" s="2"/>
     </row>
@@ -3592,10 +3614,10 @@
         <v>49</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D148" s="2"/>
     </row>
@@ -3604,13 +3626,13 @@
         <v>49</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="150">
@@ -3618,10 +3640,10 @@
         <v>49</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D150" s="2"/>
     </row>
@@ -3630,10 +3652,10 @@
         <v>49</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D151" s="2"/>
     </row>
@@ -3642,10 +3664,10 @@
         <v>49</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D152" s="2"/>
     </row>
@@ -3654,10 +3676,10 @@
         <v>49</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D153" s="2"/>
     </row>
@@ -3666,10 +3688,10 @@
         <v>49</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D154" s="2"/>
     </row>
@@ -3678,10 +3700,10 @@
         <v>49</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D155" s="2"/>
     </row>
@@ -3690,10 +3712,10 @@
         <v>49</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D156" s="2"/>
     </row>
@@ -3702,10 +3724,10 @@
         <v>49</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D157" s="2"/>
     </row>
@@ -3714,10 +3736,10 @@
         <v>49</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D158" s="2"/>
     </row>
@@ -3726,10 +3748,10 @@
         <v>49</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D159" s="2"/>
     </row>
@@ -3738,10 +3760,10 @@
         <v>49</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D160" s="2"/>
     </row>
@@ -3750,10 +3772,10 @@
         <v>49</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D161" s="2"/>
     </row>
@@ -3762,10 +3784,10 @@
         <v>49</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D162" s="2"/>
     </row>
@@ -3774,10 +3796,10 @@
         <v>49</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D163" s="2"/>
     </row>
@@ -3786,10 +3808,10 @@
         <v>49</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D164" s="2"/>
     </row>
@@ -3798,10 +3820,10 @@
         <v>49</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D165" s="2"/>
     </row>
@@ -3810,10 +3832,10 @@
         <v>49</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D166" s="2"/>
     </row>
@@ -3822,10 +3844,10 @@
         <v>49</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D167" s="2"/>
     </row>
@@ -3834,10 +3856,10 @@
         <v>49</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D168" s="2"/>
     </row>
@@ -3846,10 +3868,10 @@
         <v>49</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D169" s="2"/>
     </row>
@@ -3858,10 +3880,10 @@
         <v>49</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D170" s="2"/>
     </row>
@@ -3870,10 +3892,10 @@
         <v>49</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D171" s="2"/>
     </row>
@@ -3882,10 +3904,10 @@
         <v>49</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D172" s="2"/>
     </row>
@@ -3894,10 +3916,10 @@
         <v>49</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D173" s="2"/>
     </row>
@@ -3906,10 +3928,10 @@
         <v>49</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D174" s="2"/>
     </row>
@@ -3918,10 +3940,10 @@
         <v>49</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D175" s="2"/>
     </row>
@@ -3930,10 +3952,10 @@
         <v>49</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D176" s="2"/>
     </row>
@@ -3942,10 +3964,10 @@
         <v>49</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D177" s="2"/>
     </row>
@@ -3954,10 +3976,10 @@
         <v>49</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D178" s="2"/>
     </row>
@@ -3966,10 +3988,10 @@
         <v>49</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D179" s="2"/>
     </row>
@@ -3978,10 +4000,10 @@
         <v>49</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D180" s="2"/>
     </row>
@@ -3990,10 +4012,10 @@
         <v>49</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D181" s="2"/>
     </row>
@@ -4002,10 +4024,10 @@
         <v>49</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D182" s="2"/>
     </row>
@@ -4014,10 +4036,10 @@
         <v>49</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D183" s="2"/>
     </row>
@@ -4026,10 +4048,10 @@
         <v>49</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D184" s="2"/>
     </row>
@@ -4038,10 +4060,10 @@
         <v>49</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -4050,10 +4072,10 @@
         <v>49</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D186" s="2"/>
     </row>
@@ -4062,10 +4084,10 @@
         <v>49</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D187" s="2"/>
     </row>
@@ -4074,10 +4096,10 @@
         <v>49</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D188" s="2"/>
     </row>
@@ -4086,10 +4108,10 @@
         <v>49</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D189" s="2"/>
     </row>
@@ -4098,10 +4120,10 @@
         <v>49</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D190" s="2"/>
     </row>
@@ -4110,10 +4132,10 @@
         <v>49</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D191" s="2"/>
     </row>
@@ -4122,10 +4144,10 @@
         <v>49</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D192" s="2"/>
     </row>
@@ -4134,13 +4156,13 @@
         <v>49</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D193" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="194">
@@ -4148,10 +4170,10 @@
         <v>49</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D194" s="2"/>
     </row>
@@ -4160,10 +4182,10 @@
         <v>49</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D195" s="2"/>
     </row>
@@ -4172,10 +4194,10 @@
         <v>49</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D196" s="2"/>
     </row>
@@ -4184,10 +4206,10 @@
         <v>49</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D197" s="2"/>
     </row>
@@ -4196,10 +4218,10 @@
         <v>49</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D198" s="2"/>
     </row>
@@ -4208,10 +4230,10 @@
         <v>49</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D199" s="2"/>
     </row>
@@ -4220,13 +4242,13 @@
         <v>49</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D200" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="201">
@@ -4234,13 +4256,13 @@
         <v>49</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D201" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="202">
@@ -4248,13 +4270,13 @@
         <v>49</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D202" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="203">
@@ -4262,13 +4284,13 @@
         <v>49</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D203" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="204">
@@ -4276,13 +4298,13 @@
         <v>49</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D204" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="205">
@@ -4290,10 +4312,10 @@
         <v>49</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D205" s="2"/>
     </row>
@@ -4302,10 +4324,10 @@
         <v>49</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D206" s="2"/>
     </row>
@@ -4314,10 +4336,10 @@
         <v>49</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D207" s="2"/>
     </row>
@@ -4326,10 +4348,10 @@
         <v>49</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -4338,10 +4360,10 @@
         <v>49</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -4350,10 +4372,10 @@
         <v>49</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -4362,12 +4384,36 @@
         <v>49</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D211" s="2"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C212" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="D212" s="2"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C213" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="D213" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
